--- a/docs/collections/goethe/metadata/data.xlsx
+++ b/docs/collections/goethe/metadata/data.xlsx
@@ -439,7 +439,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>備考</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -661,7 +661,8 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ゲーテ自署付書簡[Letter] 1822 De[zem]ber 29, Weimar [to L. W. Cramer](WA IV-36, S.249対応)</t>
+          <t>ゲーテ自署付書簡[Letter] 1822 De[zem]ber 29, Weimar [to L. W. Cramer](WA IV-36, S.249対応)
+Der Brief von Goethe an Ludwig Wilhelm Cramer vom 29. Dezember 1822 im Besitz der Universitätsbibliothek Tokio</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -681,7 +682,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://nakamura196.github.io/goethe/viewer/</t>
+          <t>https://utda.github.io/goethe/</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">

--- a/docs/collections/goethe/metadata/data.xlsx
+++ b/docs/collections/goethe/metadata/data.xlsx
@@ -661,7 +661,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ゲーテ自署付書簡[Letter] 1822 De[zem]ber 29, Weimar [to L. W. Cramer](WA IV-36, S.249対応)
+          <t>ゲーテ自署付書簡[Letter] 1822 Dcbr. 29, Weimar [to L. W. Cramer](WA IV-36, S.249対応)
 Der Brief von Goethe an Ludwig Wilhelm Cramer vom 29. Dezember 1822 im Besitz der Universitätsbibliothek Tokio</t>
         </is>
       </c>

--- a/docs/collections/goethe/metadata/data.xlsx
+++ b/docs/collections/goethe/metadata/data.xlsx
@@ -661,7 +661,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ゲーテ自署付書簡[Letter] 1822 Dcbr. 29, Weimar [to L. W. Cramer](WA IV-36, S.249対応)
+          <t>ゲーテ自署付書簡[Letter] 1822 Dcbr. 29, Weimar [to L. W. Cramer](WA IV-36, S. 249対応)
 Der Brief von Goethe an Ludwig Wilhelm Cramer vom 29. Dezember 1822 im Besitz der Universitätsbibliothek Tokio</t>
         </is>
       </c>

--- a/docs/collections/goethe/metadata/data.xlsx
+++ b/docs/collections/goethe/metadata/data.xlsx
@@ -661,7 +661,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ゲーテ自署付書簡[Letter] 1822 Dcbr. 29, Weimar [to L. W. Cramer](WA IV-36, S. 249対応)
+          <t>ゲーテ自署付書簡 [Letter] Weimar, 29. Dcbr. 1822 [to L. W. Cramer](WA IV-36, S. 249対応)
 Der Brief von Goethe an Ludwig Wilhelm Cramer vom 29. Dezember 1822 im Besitz der Universitätsbibliothek Tokio</t>
         </is>
       </c>
